--- a/forms/kobo_xlsform_menage.xlsx
+++ b/forms/kobo_xlsform_menage.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Rc92651b6bce14c28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R4cb0fb0c2782409a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Rf09c5d75c5084670"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R1f8e71bb2db54bc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R6f63df05a9ad49f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Rc7f9cf971e494abc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -561,7 +561,9 @@
       <x:c r="G4" s="11"/>
       <x:c r="H4" s="11"/>
       <x:c r="I4" s="11"/>
-      <x:c r="J4" s="28"/>
+      <x:c r="J4" s="28" t="str">
+        <x:v>field-list</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="20" customHeight="1">
       <x:c r="A5" s="29" t="str">
@@ -605,24 +607,24 @@
     </x:row>
     <x:row r="7" ht="20" customHeight="1">
       <x:c r="A7" s="25" t="str">
-        <x:v>text</x:v>
+        <x:v>calculate</x:v>
       </x:c>
       <x:c r="B7" s="7" t="str">
         <x:v>household_id</x:v>
       </x:c>
       <x:c r="C7" s="7" t="str">
-        <x:v>Identifiant unique du ménage</x:v>
+        <x:v>Identifiant automatique du ménage</x:v>
       </x:c>
       <x:c r="D7" s="7" t="str">
-        <x:v>Ex. MEN-001</x:v>
-      </x:c>
-      <x:c r="E7" s="7" t="str">
-        <x:v>yes</x:v>
-      </x:c>
+        <x:v>Généré automatiquement à partir du projet, de la date et d’un identifiant unique.</x:v>
+      </x:c>
+      <x:c r="E7" s="7"/>
       <x:c r="F7" s="7"/>
       <x:c r="G7" s="7"/>
       <x:c r="H7" s="7"/>
-      <x:c r="I7" s="7"/>
+      <x:c r="I7" s="7" t="str">
+        <x:v>once(concat(${project_code}, '-', format-date(today(), '%Y%m%d'), '-', uuid(6)))</x:v>
+      </x:c>
       <x:c r="J7" s="26"/>
     </x:row>
     <x:row r="8" ht="20" customHeight="1">
@@ -734,9 +736,7 @@
         <x:v>Position GPS du ménage</x:v>
       </x:c>
       <x:c r="D13" s="7"/>
-      <x:c r="E13" s="7" t="str">
-        <x:v>yes</x:v>
-      </x:c>
+      <x:c r="E13" s="7"/>
       <x:c r="F13" s="7"/>
       <x:c r="G13" s="7"/>
       <x:c r="H13" s="7"/>
@@ -775,7 +775,9 @@
       <x:c r="G15" s="11"/>
       <x:c r="H15" s="11"/>
       <x:c r="I15" s="11"/>
-      <x:c r="J15" s="28"/>
+      <x:c r="J15" s="28" t="str">
+        <x:v>field-list</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="20" customHeight="1">
       <x:c r="A16" s="25" t="str">
@@ -999,7 +1001,9 @@
       <x:c r="G26" s="18"/>
       <x:c r="H26" s="18"/>
       <x:c r="I26" s="18"/>
-      <x:c r="J26" s="36"/>
+      <x:c r="J26" s="36" t="str">
+        <x:v>field-list</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="20" customHeight="1">
       <x:c r="A27" s="25" t="str">
@@ -1569,7 +1573,9 @@
       <x:c r="G56" s="14"/>
       <x:c r="H56" s="14"/>
       <x:c r="I56" s="14"/>
-      <x:c r="J56" s="32"/>
+      <x:c r="J56" s="32" t="str">
+        <x:v>field-list</x:v>
+      </x:c>
     </x:row>
     <x:row r="57" ht="24" customHeight="1">
       <x:c r="A57" s="27" t="str">
@@ -1671,7 +1677,9 @@
       <x:c r="G61" s="7"/>
       <x:c r="H61" s="7"/>
       <x:c r="I61" s="7"/>
-      <x:c r="J61" s="26"/>
+      <x:c r="J61" s="26" t="str">
+        <x:v>field-list</x:v>
+      </x:c>
     </x:row>
     <x:row r="62" ht="20" customHeight="1">
       <x:c r="A62" s="31" t="str">
@@ -1763,7 +1771,9 @@
       <x:c r="G66" s="7"/>
       <x:c r="H66" s="7"/>
       <x:c r="I66" s="7"/>
-      <x:c r="J66" s="26"/>
+      <x:c r="J66" s="26" t="str">
+        <x:v>field-list</x:v>
+      </x:c>
     </x:row>
     <x:row r="67" ht="20" customHeight="1">
       <x:c r="A67" s="31" t="str">
@@ -1857,7 +1867,9 @@
       <x:c r="G71" s="7"/>
       <x:c r="H71" s="7"/>
       <x:c r="I71" s="7"/>
-      <x:c r="J71" s="26"/>
+      <x:c r="J71" s="26" t="str">
+        <x:v>field-list</x:v>
+      </x:c>
     </x:row>
     <x:row r="72" ht="20" customHeight="1">
       <x:c r="A72" s="31" t="str">
@@ -1999,7 +2011,9 @@
       <x:c r="I78" s="16" t="str">
         <x:v>${monthly_income} - ${monthly_expenses}</x:v>
       </x:c>
-      <x:c r="J78" s="34"/>
+      <x:c r="J78" s="34" t="str">
+        <x:v>field-list</x:v>
+      </x:c>
     </x:row>
     <x:row r="79" ht="20" customHeight="1">
       <x:c r="A79" s="23" t="str">
@@ -2131,7 +2145,9 @@
       <x:c r="G85" s="7"/>
       <x:c r="H85" s="7"/>
       <x:c r="I85" s="7"/>
-      <x:c r="J85" s="26"/>
+      <x:c r="J85" s="26" t="str">
+        <x:v>field-list</x:v>
+      </x:c>
     </x:row>
     <x:row r="86" ht="20" customHeight="1">
       <x:c r="A86" s="25" t="str">
@@ -3261,7 +3277,7 @@
         <x:v>kobo_menage_detaille</x:v>
       </x:c>
       <x:c r="C2" s="46" t="str">
-        <x:v>v3</x:v>
+        <x:v>v4</x:v>
       </x:c>
       <x:c r="D2" s="46" t="str">
         <x:v>Français</x:v>
